--- a/Data Files/Auto/RenovacoesSantanderData/TabCap.xlsx
+++ b/Data Files/Auto/RenovacoesSantanderData/TabCap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Auto\RenovacoesSantanderData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878B1FE5-6BDF-4DE4-83CF-9B111640D63F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8198B960-5DEC-4C9C-9CCA-105792AF9246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -854,7 +854,7 @@
         <v>0.3</v>
       </c>
       <c r="E15" s="6">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
